--- a/data/trans_camb/IP1004-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1004-Clase-trans_camb.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,66</t>
+          <t>0,0; 4,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,39</t>
+          <t>0,0; 4,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,05</t>
+          <t>0,0; 2,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -787,12 +787,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 0,0</t>
+          <t>-5,32; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 0,0</t>
+          <t>-4,89; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 0,0</t>
+          <t>-2,84; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 0,0</t>
+          <t>-2,87; 0,0</t>
         </is>
       </c>
     </row>
@@ -953,22 +953,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 0,0</t>
+          <t>-3,14; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 0,0</t>
+          <t>-3,12; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 0,0</t>
+          <t>-2,4; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 0,0</t>
+          <t>-2,05; 0,0</t>
         </is>
       </c>
     </row>
@@ -1104,27 +1104,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,9</t>
+          <t>0,0; 1,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 0,66</t>
+          <t>-1,0; 0,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 0,0</t>
+          <t>-1,65; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,69</t>
+          <t>-0,33; 0,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,54</t>
+          <t>-0,33; 0,55</t>
         </is>
       </c>
     </row>
@@ -1265,17 +1265,17 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,31; -0,46</t>
+          <t>-4,11; -0,47</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,3; -0,46</t>
+          <t>-4,11; -0,47</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,44; -0,26</t>
+          <t>-2,29; -0,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,8</t>
+          <t>0,0; 4,9</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,0; 2,51</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,25</t>
+          <t>-0,54; 0,34</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,33</t>
+          <t>-0,46; 0,38</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 0,2</t>
+          <t>-0,77; 0,24</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,04; -0,18</t>
+          <t>-1,03; -0,17</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 0,17</t>
+          <t>-0,54; 0,13</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,01</t>
+          <t>-0,62; 0,0</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 384,36</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -1663,12 +1663,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 165,58</t>
+          <t>-100,0; 104,89</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 87,83</t>
+          <t>-100,0; 132,18</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1004-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1004-Clase-trans_camb.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,54</t>
+          <t>0,0; 4,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,67</t>
+          <t>0,0; 4,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,67</t>
+          <t>0,0; 3,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -787,12 +787,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 0,0</t>
+          <t>-4,96; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 0,0</t>
+          <t>-4,97; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 0,0</t>
+          <t>-2,73; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 0,0</t>
+          <t>-2,75; 0,0</t>
         </is>
       </c>
     </row>
@@ -953,22 +953,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 0,0</t>
+          <t>-3,43; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 0,0</t>
+          <t>-3,67; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 0,0</t>
+          <t>-1,88; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 0,0</t>
+          <t>-1,52; 0,0</t>
         </is>
       </c>
     </row>
@@ -1104,27 +1104,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,39</t>
+          <t>0,0; 1,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 0,66</t>
+          <t>-1,0; 0,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 0,0</t>
+          <t>-1,38; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
+          <t>-0,33; 0,52</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
           <t>-0,33; 0,53</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-0,33; 0,55</t>
         </is>
       </c>
     </row>
@@ -1265,22 +1265,22 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,11; -0,47</t>
+          <t>-4,12; -0,47</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,11; -0,47</t>
+          <t>-4,38; -0,47</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,29; -0,26</t>
+          <t>-2,27; -0,25</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,34; -0,26</t>
+          <t>-2,31; -0,25</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,51</t>
+          <t>0,0; 2,31</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 0,34</t>
+          <t>-0,45; 0,24</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,38</t>
+          <t>-0,45; 0,38</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,24</t>
+          <t>-0,79; 0,24</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,03; -0,17</t>
+          <t>-1,02; -0,18</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 0,13</t>
+          <t>-0,52; 0,11</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 0,0</t>
+          <t>-0,57; 0,01</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 384,36</t>
+          <t>-100,0; 297,49</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -1663,12 +1663,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 104,89</t>
+          <t>-100,0; 88,95</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 132,18</t>
+          <t>-100,0; 93,11</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1004-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1004-Clase-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,17 +593,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,87</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,89</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,87</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,51</t>
+          <t>0,0; 4,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,06</t>
+          <t>0,0; 4,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,1</t>
+          <t>0,0; 3,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-1,62</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>-1,62</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,62; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,62; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 0,0</t>
+          <t>-2,53; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 0,0</t>
+          <t>-2,47; 0,0</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,62</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,62</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,62</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,62</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,55; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,46; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 0,0</t>
+          <t>-1,85; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 0,0</t>
+          <t>-1,87; 0,0</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,33</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>0,34</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,33</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,32; 0,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,73</t>
+          <t>-2,13; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 0,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 0,0</t>
+          <t>0,0; 1,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,52</t>
+          <t>-0,33; 0,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,53</t>
+          <t>-0,33; 0,54</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-0,62%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-0,62%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-1,55</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-1,55</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-1,55</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-1,55</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,31; -0,46</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,3; -0,46</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,12; -0,47</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,38; -0,47</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,27; -0,25</t>
+          <t>-2,44; -0,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,31; -0,25</t>
+          <t>-2,34; -0,26</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1378,17 +1378,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>0,96</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,8</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,31</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
     </row>
@@ -1454,17 +1454,17 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-0,26</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-0,48</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>-0,1</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>-0,02</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-0,26</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-0,48</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,24</t>
+          <t>-0,78; 0,2</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,38</t>
+          <t>-1,04; -0,18</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 0,24</t>
+          <t>-0,45; 0,25</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,02; -0,18</t>
+          <t>-0,45; 0,33</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 0,11</t>
+          <t>-0,54; 0,17</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 0,01</t>
+          <t>-0,64; 0,01</t>
         </is>
       </c>
     </row>
@@ -1605,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-55,14%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>-47,07%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>-8,55%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-55,14%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 297,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -1663,12 +1663,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 88,95</t>
+          <t>-100,0; 165,58</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 93,11</t>
+          <t>-100,0; 87,83</t>
         </is>
       </c>
     </row>
